--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DFS_HRM-2031-0192/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DFS_HRM-2031-0192/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.67382</v>
+        <v>16.76339</v>
       </c>
       <c r="D2" t="n">
-        <v>17.02935</v>
+        <v>16.71521</v>
       </c>
       <c r="E2" t="n">
-        <v>16.99572</v>
+        <v>16.73561</v>
       </c>
       <c r="F2" t="n">
-        <v>44.16937</v>
+        <v>43.50165</v>
       </c>
       <c r="G2" t="n">
         <v>0.05091</v>
       </c>
       <c r="H2" t="n">
-        <v>1.86358</v>
+        <v>1.83974</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.89228</v>
+        <v>17.39561</v>
       </c>
       <c r="D3" t="n">
-        <v>16.93199</v>
+        <v>16.63517</v>
       </c>
       <c r="E3" t="n">
-        <v>17.1069</v>
+        <v>17.22726</v>
       </c>
       <c r="F3" t="n">
-        <v>43.40865</v>
+        <v>42.09739</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05181</v>
+        <v>0.05112</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80876</v>
+        <v>1.81898</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.06571</v>
+        <v>16.91922</v>
       </c>
       <c r="D4" t="n">
-        <v>16.92562</v>
+        <v>16.68519</v>
       </c>
       <c r="E4" t="n">
-        <v>16.75304</v>
+        <v>16.73433</v>
       </c>
       <c r="F4" t="n">
-        <v>43.62212</v>
+        <v>43.23358</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0517</v>
+        <v>0.05127</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82265</v>
+        <v>1.86354</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.75883</v>
+        <v>17.06847</v>
       </c>
       <c r="D5" t="n">
-        <v>16.79186</v>
+        <v>16.87065</v>
       </c>
       <c r="E5" t="n">
-        <v>16.65036</v>
+        <v>16.89044</v>
       </c>
       <c r="F5" t="n">
-        <v>43.22554</v>
+        <v>42.90225</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04972</v>
+        <v>0.05196</v>
       </c>
       <c r="H5" t="n">
-        <v>1.83455</v>
+        <v>1.83832</v>
       </c>
     </row>
     <row r="6">
@@ -559,23 +559,10 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>16.80213</v>
-      </c>
-      <c r="D6" t="n">
-        <v>16.63544</v>
-      </c>
-      <c r="E6" t="n">
-        <v>17.0518</v>
-      </c>
-      <c r="F6" t="n">
-        <v>42.71718</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.05244</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.86006</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>scratched - not measurable</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -585,22 +572,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.83797</v>
+        <v>17.30413</v>
       </c>
       <c r="D7" t="n">
-        <v>17.20387</v>
+        <v>16.66923</v>
       </c>
       <c r="E7" t="n">
-        <v>16.76725</v>
+        <v>17.1112</v>
       </c>
       <c r="F7" t="n">
-        <v>43.20916</v>
+        <v>43.2928</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05</v>
+        <v>0.05144</v>
       </c>
       <c r="H7" t="n">
-        <v>1.82785</v>
+        <v>1.8194</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +597,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.29251</v>
+        <v>16.91031</v>
       </c>
       <c r="D8" t="n">
-        <v>16.65061</v>
+        <v>16.41491</v>
       </c>
       <c r="E8" t="n">
-        <v>17.17648</v>
+        <v>16.71293</v>
       </c>
       <c r="F8" t="n">
-        <v>43.45138</v>
+        <v>43.20923</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05075</v>
+        <v>0.05164</v>
       </c>
       <c r="H8" t="n">
-        <v>1.83091</v>
+        <v>1.84813</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +622,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.92584</v>
+        <v>16.80132</v>
       </c>
       <c r="D9" t="n">
-        <v>16.72905</v>
+        <v>16.6053</v>
       </c>
       <c r="E9" t="n">
-        <v>16.79449</v>
+        <v>16.78247</v>
       </c>
       <c r="F9" t="n">
-        <v>42.91134</v>
+        <v>43.2625</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05071</v>
+        <v>0.05179</v>
       </c>
       <c r="H9" t="n">
-        <v>1.87469</v>
+        <v>1.88375</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +647,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.05139</v>
+        <v>17.08946</v>
       </c>
       <c r="D10" t="n">
-        <v>16.71964</v>
+        <v>16.65209</v>
       </c>
       <c r="E10" t="n">
-        <v>17.01507</v>
+        <v>16.93141</v>
       </c>
       <c r="F10" t="n">
-        <v>42.91586</v>
+        <v>43.06899</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05141</v>
+        <v>0.05007</v>
       </c>
       <c r="H10" t="n">
-        <v>1.84034</v>
+        <v>1.81805</v>
       </c>
     </row>
     <row r="11">
@@ -716,6 +703,21 @@
           <t>Trace 1</t>
         </is>
       </c>
+      <c r="C12" t="n">
+        <v>16.7246</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16.14861</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="F12" t="n">
+        <v>21.81241</v>
+      </c>
+      <c r="G12" t="n">
+        <v>34.02684</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -723,6 +725,21 @@
           <t>Unit 8</t>
         </is>
       </c>
+      <c r="C13" t="n">
+        <v>16.90867</v>
+      </c>
+      <c r="D13" t="n">
+        <v>15.90032</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.5847</v>
+      </c>
+      <c r="F13" t="n">
+        <v>22.24811</v>
+      </c>
+      <c r="G13" t="n">
+        <v>35.11612</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -730,6 +747,26 @@
           <t>Unit 9</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>re-measured</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>16.72897</v>
+      </c>
+      <c r="D14" t="n">
+        <v>15.87804</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.50664</v>
+      </c>
+      <c r="F14" t="n">
+        <v>22.05932</v>
+      </c>
+      <c r="G14" t="n">
+        <v>34.8832</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -737,6 +774,21 @@
           <t>Unit 4</t>
         </is>
       </c>
+      <c r="C15" t="n">
+        <v>17.08209</v>
+      </c>
+      <c r="D15" t="n">
+        <v>16.09469</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.57799</v>
+      </c>
+      <c r="F15" t="n">
+        <v>21.91984</v>
+      </c>
+      <c r="G15" t="n">
+        <v>34.7444</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -744,6 +796,21 @@
           <t>Unit 5</t>
         </is>
       </c>
+      <c r="C16" t="n">
+        <v>16.9355</v>
+      </c>
+      <c r="D16" t="n">
+        <v>15.7369</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.74486</v>
+      </c>
+      <c r="F16" t="n">
+        <v>22.22785</v>
+      </c>
+      <c r="G16" t="n">
+        <v>34.89193</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -751,6 +818,21 @@
           <t>Unit 6</t>
         </is>
       </c>
+      <c r="C17" t="n">
+        <v>16.9715</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16.24185</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.56941</v>
+      </c>
+      <c r="F17" t="n">
+        <v>21.82522</v>
+      </c>
+      <c r="G17" t="n">
+        <v>34.3927</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -758,6 +840,21 @@
           <t>Unit 1</t>
         </is>
       </c>
+      <c r="C18" t="n">
+        <v>16.9007</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16.00448</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.65972</v>
+      </c>
+      <c r="F18" t="n">
+        <v>21.57535</v>
+      </c>
+      <c r="G18" t="n">
+        <v>34.54671</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -765,12 +862,42 @@
           <t>Unit 2</t>
         </is>
       </c>
+      <c r="C19" t="n">
+        <v>16.83443</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16.30262</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.71366</v>
+      </c>
+      <c r="F19" t="n">
+        <v>21.91245</v>
+      </c>
+      <c r="G19" t="n">
+        <v>34.06805</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>Unit 3</t>
         </is>
+      </c>
+      <c r="C20" t="n">
+        <v>16.56059</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.25407</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.50347</v>
+      </c>
+      <c r="F20" t="n">
+        <v>21.9833</v>
+      </c>
+      <c r="G20" t="n">
+        <v>35.03787</v>
       </c>
     </row>
   </sheetData>
